--- a/Data/Input/DemoQA_Input.xlsx
+++ b/Data/Input/DemoQA_Input.xlsx
@@ -8,24 +8,35 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Test\DemoQa_Form_Automation\Data\Input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF534D66-689F-4178-B2A1-75150EBCE3BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{768136C2-504C-42C4-A919-B23928941653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="116">
   <si>
     <t>FirstName</t>
   </si>
@@ -78,9 +89,6 @@
     <t>Jane</t>
   </si>
   <si>
-    <t>Smith</t>
-  </si>
-  <si>
     <t>jane.smith@gmail.com</t>
   </si>
   <si>
@@ -120,9 +128,6 @@
     <t>Wilson</t>
   </si>
   <si>
-    <t>sarah.wilson@gmail.com</t>
-  </si>
-  <si>
     <t>English,History</t>
   </si>
   <si>
@@ -132,12 +137,6 @@
     <t>Khon Kaen Thailand</t>
   </si>
   <si>
-    <t>David</t>
-  </si>
-  <si>
-    <t>Lee</t>
-  </si>
-  <si>
     <t>david.lee@gmail.com</t>
   </si>
   <si>
@@ -207,9 +206,6 @@
     <t>Anderson</t>
   </si>
   <si>
-    <t>tom.andersongmail.com</t>
-  </si>
-  <si>
     <t>Lisa</t>
   </si>
   <si>
@@ -228,9 +224,6 @@
     <t>0812345678</t>
   </si>
   <si>
-    <t>0898765432</t>
-  </si>
-  <si>
     <t>0823456789</t>
   </si>
   <si>
@@ -252,9 +245,6 @@
     <t>0889012345</t>
   </si>
   <si>
-    <t>012345</t>
-  </si>
-  <si>
     <t>Robert</t>
   </si>
   <si>
@@ -264,24 +254,12 @@
     <t>Physics</t>
   </si>
   <si>
-    <t>Green</t>
-  </si>
-  <si>
-    <t>green@gmail.com</t>
-  </si>
-  <si>
     <t>Jennifer</t>
   </si>
   <si>
     <t>jennifer@gmail.com</t>
   </si>
   <si>
-    <t>0891234567</t>
-  </si>
-  <si>
-    <t>0861234567</t>
-  </si>
-  <si>
     <t>lisa.miller@gmailcom</t>
   </si>
   <si>
@@ -291,18 +269,12 @@
     <t>Harris</t>
   </si>
   <si>
-    <t>robertwhitegmailcom</t>
-  </si>
-  <si>
     <t>Daniel</t>
   </si>
   <si>
     <t>Clark</t>
   </si>
   <si>
-    <t>daniel.clark@gmail.com</t>
-  </si>
-  <si>
     <t>Sophia</t>
   </si>
   <si>
@@ -312,18 +284,9 @@
     <t>sophia.walker@gmail.com</t>
   </si>
   <si>
-    <t>noemail</t>
-  </si>
-  <si>
     <t>King</t>
   </si>
   <si>
-    <t>kinggmail.com</t>
-  </si>
-  <si>
-    <t>ethanharris@gmailcom</t>
-  </si>
-  <si>
     <t>Ayutthaya Thailand</t>
   </si>
   <si>
@@ -339,28 +302,88 @@
     <t>History</t>
   </si>
   <si>
-    <t>Test Address</t>
-  </si>
-  <si>
     <t>0123456789</t>
   </si>
   <si>
-    <t>012345678901</t>
-  </si>
-  <si>
-    <t>0890123456</t>
-  </si>
-  <si>
-    <t>081234567</t>
-  </si>
-  <si>
-    <t>08123456789</t>
-  </si>
-  <si>
     <t>Reading,Sports</t>
   </si>
   <si>
     <t>Music,Sports</t>
+  </si>
+  <si>
+    <t>ethan.harris@gmail.com</t>
+  </si>
+  <si>
+    <t>tom.anderson@gmail.com</t>
+  </si>
+  <si>
+    <t>robert.white@gmail.com</t>
+  </si>
+  <si>
+    <t>king@gmail.com</t>
+  </si>
+  <si>
+    <t>Kevin</t>
+  </si>
+  <si>
+    <t>Moore</t>
+  </si>
+  <si>
+    <t>kevin.gmail.com</t>
+  </si>
+  <si>
+    <t>Garcia</t>
+  </si>
+  <si>
+    <t>daniel@gmail.com</t>
+  </si>
+  <si>
+    <t>08ABCD1234</t>
+  </si>
+  <si>
+    <t>Grace</t>
+  </si>
+  <si>
+    <t>Hall</t>
+  </si>
+  <si>
+    <t>grace.hall@gmail.com</t>
+  </si>
+  <si>
+    <t>Ryan</t>
+  </si>
+  <si>
+    <t>Scott</t>
+  </si>
+  <si>
+    <t>abc@gmail</t>
+  </si>
+  <si>
+    <t>Hannah</t>
+  </si>
+  <si>
+    <t>Adams</t>
+  </si>
+  <si>
+    <t>hannah@gmail.com</t>
+  </si>
+  <si>
+    <t>0801234567</t>
+  </si>
+  <si>
+    <t>0811111111</t>
+  </si>
+  <si>
+    <t>0822222222</t>
+  </si>
+  <si>
+    <t>0833333333</t>
+  </si>
+  <si>
+    <t>0844444444</t>
+  </si>
+  <si>
+    <t>0855555555</t>
   </si>
 </sst>
 </file>
@@ -368,7 +391,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="173" formatCode="d\ mmm\ yyyy"/>
+    <numFmt numFmtId="164" formatCode="d\ mmm\ yyyy"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -427,28 +450,28 @@
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -730,18 +753,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="11.5703125" style="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="26.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.5703125" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.28515625" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="26.85546875" style="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -774,531 +797,562 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E2" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="F2" s="9">
+        <v>34714</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" s="4"/>
+      <c r="D3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="F3" s="9">
+        <v>35876</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4" s="9">
+        <v>34128</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="F5" s="9">
+        <v>35690</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="F6" s="9">
+        <v>34668</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6" s="2"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="F2" s="8">
-        <v>32947</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="3" t="s">
+      <c r="F7" s="9">
+        <v>35100</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D8" s="2"/>
+      <c r="E8" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="F8" s="9">
+        <v>33828</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="F9" s="9">
+        <v>33356</v>
+      </c>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="6"/>
+      <c r="F10" s="9">
+        <v>36355</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="F11" s="9"/>
+      <c r="G11" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="5"/>
-      <c r="B3" s="3" t="s">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="4"/>
+      <c r="B12" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="F12" s="9">
+        <v>34839</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="4"/>
+      <c r="C13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="F13" s="9">
+        <v>35721</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" s="4"/>
+      <c r="F14" s="9">
+        <v>34345</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="F15" s="9">
+        <v>34053</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="B16" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="C16" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="F16" s="9">
+        <v>35955</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" s="2">
+        <v>12345678901</v>
+      </c>
+      <c r="F17" s="9">
+        <v>35277</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F18" s="9">
+        <v>34805</v>
+      </c>
+      <c r="G18" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="F3" s="8">
-        <v>34710</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H3" s="3" t="s">
+      <c r="H18" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="F19" s="9">
+        <v>33874</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="I3" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="F4" s="8">
-        <v>33729</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D5" s="3" t="s">
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="F5" s="8">
-        <v>33594</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="5"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="F6" s="8">
-        <v>32874</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="5"/>
-      <c r="B7" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="F7" s="8">
-        <v>33897</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="F8" s="8">
-        <v>34564</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="F9" s="8">
-        <v>34001</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="F10" s="8">
-        <v>35258</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="F11" s="8">
-        <v>34104</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="F12" s="8">
-        <v>33141</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E13" s="6" t="s">
+      <c r="E20" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="F20" s="9">
+        <v>33575</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="F13" s="8">
-        <v>35764</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="F14" s="8">
-        <v>32612</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E15" s="6" t="s">
+      <c r="B21" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="F15" s="8">
-        <v>33300</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E16" s="6" t="s">
+      <c r="C21" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="F16" s="8">
-        <v>33824</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="B17" s="5"/>
-      <c r="C17" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="F17" s="8">
-        <v>34522</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C18" s="4" t="s">
+      <c r="D21" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="F18" s="8">
-        <v>34870</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="F19" s="8">
-        <v>32152</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>28</v>
+      <c r="E21" s="2">
+        <v>8123</v>
+      </c>
+      <c r="F21" s="9">
+        <v>36212</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" display="mailto:john.doe@gmail.com" xr:uid="{416C9E9C-2ECD-4643-8D97-FC2DA293CF0C}"/>
-    <hyperlink ref="C18" r:id="rId2" display="mailto:jane.smith@gmail.com" xr:uid="{B96E3677-9CF8-495C-8694-7BA892AA6776}"/>
-    <hyperlink ref="C19" r:id="rId3" display="mailto:michael.brown@gmail.com" xr:uid="{60952CCB-B34C-499E-81E6-D8AD374B382B}"/>
-    <hyperlink ref="C4" r:id="rId4" display="mailto:sarah.wilson@gmail.com" xr:uid="{83D28CA6-4929-4344-9970-6CA5E2504EB8}"/>
-    <hyperlink ref="C5" r:id="rId5" display="mailto:david.lee@gmail.com" xr:uid="{4E4C20E8-4CC4-4289-BC8D-2AAB6A3CC724}"/>
-    <hyperlink ref="C8" r:id="rId6" display="mailto:emma.taylor@gmail.com" xr:uid="{ED4EF9F0-40A3-49A3-B387-328465524E52}"/>
-    <hyperlink ref="C9" r:id="rId7" display="mailto:chris.johnson@gmail.com" xr:uid="{9F9E460D-B500-4075-97F8-2BD39D5E8A06}"/>
-    <hyperlink ref="C10" r:id="rId8" display="mailto:olivia.davis@gmail.com" xr:uid="{835F0BDF-C9D7-409D-9CEE-1DC0320588A4}"/>
-    <hyperlink ref="C15" r:id="rId9" display="mailto:daniel.clark@gmail.com" xr:uid="{49B24D32-0227-4B27-A8F9-055492C44262}"/>
-    <hyperlink ref="C16" r:id="rId10" display="mailto:sophia.walker@gmail.com" xr:uid="{5605B59B-85E3-40CF-A784-8688B9E5889D}"/>
-    <hyperlink ref="C3" r:id="rId11" display="mailto:green@gmail.com" xr:uid="{28E9E88F-DD31-4076-8715-D59F192A99DA}"/>
-    <hyperlink ref="C17" r:id="rId12" display="mailto:jennifer@gmail.com" xr:uid="{C8BFDEEF-C169-4FA2-8C35-0A5FBE20C824}"/>
+    <hyperlink ref="C21" r:id="rId1" display="mailto:hannah@gmail.com" xr:uid="{543AF9C1-40D4-4727-8404-5A5E57787B26}"/>
+    <hyperlink ref="C19" r:id="rId2" display="mailto:grace.hall@gmail.com" xr:uid="{01A70368-C51F-43B8-87F5-C4CE724F6530}"/>
+    <hyperlink ref="C18" r:id="rId3" display="mailto:daniel@gmail.com" xr:uid="{20E10AE8-2D40-4EB7-A17B-5098180EE90B}"/>
+    <hyperlink ref="C17" r:id="rId4" display="mailto:jennifer@gmail.com" xr:uid="{C35323E6-C4A1-495C-83FA-1C74111E58B7}"/>
+    <hyperlink ref="C16" r:id="rId5" display="mailto:sophia.walker@gmail.com" xr:uid="{74A262B7-D810-401F-B234-92CB0B1C307F}"/>
+    <hyperlink ref="C14" r:id="rId6" display="mailto:michael.brown@gmail.com" xr:uid="{7A69F73D-D897-4FF8-88B9-D4CC18BF4FE9}"/>
+    <hyperlink ref="C13" r:id="rId7" display="mailto:jane.smith@gmail.com" xr:uid="{95D911DE-50E9-4F71-85D4-7BF0D2729310}"/>
+    <hyperlink ref="C12" r:id="rId8" display="mailto:king@gmail.com" xr:uid="{BF327ED9-91E1-4EF7-BC95-A8D13824DC6F}"/>
+    <hyperlink ref="C11" r:id="rId9" display="mailto:robert.white@gmail.com" xr:uid="{38263DC8-190A-46D4-8D0C-32ADF685247C}"/>
+    <hyperlink ref="C10" r:id="rId10" xr:uid="{865A4A4B-4961-4662-9E32-90B45EACDA5E}"/>
+    <hyperlink ref="C9" r:id="rId11" display="mailto:tom.anderson@gmail.com" xr:uid="{82FA7A10-1B28-43F5-B81F-29098E4F7FEE}"/>
+    <hyperlink ref="C8" r:id="rId12" display="mailto:ethan.harris@gmail.com" xr:uid="{C9948FF2-E7B3-40C6-9E9B-1C87AE1EAC5C}"/>
+    <hyperlink ref="C7" r:id="rId13" display="mailto:olivia.davis@gmail.com" xr:uid="{D0CCF4FD-1591-4B50-BF85-ECDE8672AA40}"/>
+    <hyperlink ref="C6" r:id="rId14" display="mailto:chris.johnson@gmail.com" xr:uid="{73E4CDE4-9407-41DA-A461-23AF55C660E1}"/>
+    <hyperlink ref="C5" r:id="rId15" display="mailto:emma.taylor@gmail.com" xr:uid="{2470F0BB-5512-4AA7-A1BA-95F09D50EBF0}"/>
+    <hyperlink ref="C4" r:id="rId16" display="mailto:david.lee@gmail.com" xr:uid="{04C69AF1-EF10-4994-955C-019302CC668F}"/>
+    <hyperlink ref="C2" r:id="rId17" display="mailto:john.doe@gmail.com" xr:uid="{88B8236B-1D8B-4439-BEF3-970D2B83C0F7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Data/Input/DemoQA_Input.xlsx
+++ b/Data/Input/DemoQA_Input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Test\DemoQa_Form_Automation\Data\Input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{768136C2-504C-42C4-A919-B23928941653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B8C35B7-C1BE-4D0B-B1C0-46E3EA50CE5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="117">
   <si>
     <t>FirstName</t>
   </si>
@@ -143,9 +143,6 @@
     <t>Maths</t>
   </si>
   <si>
-    <t>Sports,Music</t>
-  </si>
-  <si>
     <t>Pattaya Thailand</t>
   </si>
   <si>
@@ -356,9 +353,6 @@
     <t>Scott</t>
   </si>
   <si>
-    <t>abc@gmail</t>
-  </si>
-  <si>
     <t>Hannah</t>
   </si>
   <si>
@@ -384,6 +378,15 @@
   </si>
   <si>
     <t>0855555555</t>
+  </si>
+  <si>
+    <t>ryan scott@gmail.com</t>
+  </si>
+  <si>
+    <t>Sports,Music,Reading</t>
+  </si>
+  <si>
+    <t>08123</t>
   </si>
 </sst>
 </file>
@@ -447,7 +450,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -461,14 +464,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -756,15 +758,15 @@
   <dimension ref="A1:I21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.85546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12" style="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.5703125" style="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.28515625" style="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="26.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.5703125" style="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="26.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -783,7 +785,7 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
@@ -809,10 +811,10 @@
       <c r="D2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="F2" s="9">
+      <c r="E2" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F2" s="8">
         <v>34714</v>
       </c>
       <c r="G2" s="2" t="s">
@@ -836,10 +838,10 @@
       <c r="D3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="F3" s="9">
+      <c r="E3" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="F3" s="8">
         <v>35876</v>
       </c>
       <c r="G3" s="2" t="s">
@@ -861,10 +863,10 @@
       <c r="D4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="F4" s="9">
+      <c r="E4" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F4" s="8">
         <v>34128</v>
       </c>
       <c r="G4" s="2" t="s">
@@ -879,54 +881,54 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>38</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>39</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="F5" s="9">
+      <c r="E5" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F5" s="8">
         <v>35690</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>34</v>
       </c>
       <c r="H5" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="F6" s="9">
+      <c r="E6" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F6" s="8">
         <v>34668</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>31</v>
@@ -935,28 +937,28 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E7" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="F7" s="9">
+      <c r="E7" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="F7" s="8">
         <v>35100</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>34</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>21</v>
@@ -964,48 +966,48 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="C8" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D8" s="2"/>
-      <c r="E8" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="F8" s="9">
+      <c r="E8" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="F8" s="8">
         <v>33828</v>
       </c>
       <c r="G8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="I8" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>55</v>
-      </c>
       <c r="C9" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="F9" s="9">
+      <c r="E9" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F9" s="8">
         <v>33356</v>
       </c>
       <c r="G9" s="2"/>
@@ -1013,55 +1015,55 @@
         <v>26</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="C10" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="6"/>
-      <c r="F10" s="9">
+      <c r="E10" s="5"/>
+      <c r="F10" s="8">
         <v>36355</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>31</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>70</v>
-      </c>
       <c r="C11" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="F11" s="9"/>
+      <c r="E11" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="F11" s="8"/>
       <c r="G11" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="2" t="s">
@@ -1071,18 +1073,18 @@
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
       <c r="B12" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E12" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="F12" s="9">
+      <c r="E12" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="F12" s="8">
         <v>34839</v>
       </c>
       <c r="G12" s="2" t="s">
@@ -1106,20 +1108,20 @@
       <c r="D13" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E13" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="F13" s="9">
+      <c r="E13" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="F13" s="8">
         <v>35721</v>
       </c>
       <c r="G13" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H13" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="H13" s="2" t="s">
+      <c r="I13" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -1136,86 +1138,86 @@
         <v>12</v>
       </c>
       <c r="E14" s="4"/>
-      <c r="F14" s="9">
+      <c r="F14" s="8">
         <v>34345</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="C15" s="2" t="s">
         <v>96</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>97</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E15" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="F15" s="9">
+      <c r="E15" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="F15" s="8">
         <v>34053</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>26</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="C16" s="3" t="s">
         <v>80</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>81</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E16" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="F16" s="9">
+      <c r="E16" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="F16" s="8">
         <v>35955</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>72</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>73</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>18</v>
@@ -1223,14 +1225,14 @@
       <c r="E17" s="2">
         <v>12345678901</v>
       </c>
-      <c r="F17" s="9">
+      <c r="F17" s="8">
         <v>35277</v>
       </c>
       <c r="G17" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H17" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>27</v>
@@ -1238,21 +1240,21 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="C18" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="F18" s="9">
+        <v>99</v>
+      </c>
+      <c r="F18" s="8">
         <v>34805</v>
       </c>
       <c r="G18" s="2" t="s">
@@ -1267,21 +1269,21 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="C19" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>103</v>
-      </c>
       <c r="D19" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="F19" s="9">
+        <v>45</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F19" s="8">
         <v>33874</v>
       </c>
       <c r="G19" s="2" t="s">
@@ -1296,41 +1298,41 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>105</v>
-      </c>
       <c r="C20" s="2" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E20" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="F20" s="9">
+      <c r="E20" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="F20" s="8">
         <v>33575</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>107</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>109</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E21" s="2">
-        <v>8123</v>
-      </c>
-      <c r="F21" s="9">
+      <c r="E21" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="F21" s="8">
         <v>36212</v>
       </c>
     </row>
